--- a/Defect_Tracker Template_v0.1.xlsx
+++ b/Defect_Tracker Template_v0.1.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="17.5703125" defaultRowHeight="12.75"/>
   <cols>
     <col width="6.140625" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
@@ -1020,6 +1020,281 @@
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Gemini API throws 404 NOT FOUND for gemini-1.5-flash</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Replaced gemini-1.5-flash with gemini-flash-latest</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Gemini returns list instead of string causing strip() crash</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Logical</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Added safe extraction of string from dictionary/list response</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Chat Assistant crashes with contents are required</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Logical</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Added fallback string for empty prompts</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Apply Fix button fails with 404 Not Found</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Updated App.jsx to point to /api/v1/submit prefix</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>UI scales infinitely and requires excessive scrolling</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>User Interface</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Restricted app-grid height to 100vh and added internal scrolling</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
